--- a/data/trans_orig/P64S_2023_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33076</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24854</t>
+          <t>26003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>46750</t>
+          <t>49484</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59249</t>
+          <t>63409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20719</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>49192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53995</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2116,32 +2116,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2151,32 +2151,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>29706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2194,32 +2194,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>199385</t>
+          <t>212159</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178598</t>
+          <t>191752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218973</t>
+          <t>233596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2229,32 +2229,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>171576</t>
+          <t>180335</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154322</t>
+          <t>164029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186144</t>
+          <t>196352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>370961</t>
+          <t>392494</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345361</t>
+          <t>363225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395451</t>
+          <t>419081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2420,32 +2420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51230</t>
+          <t>54139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82791</t>
+          <t>86650</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2455,32 +2455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68251</t>
+          <t>72546</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81268</t>
+          <t>85007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>133431</t>
+          <t>142128</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113447</t>
+          <t>121467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155497</t>
+          <t>163645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>350802</t>
+          <t>381669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312594</t>
+          <t>333100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>663396</t>
+          <t>714769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>46487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3554,32 +3554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3589,32 +3589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3624,32 +3624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>698</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3815,32 +3815,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>20159</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27197</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>44405</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4041,32 +4041,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4119,32 +4119,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>199068</t>
+          <t>208677</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>179903</t>
+          <t>188565</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>215061</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>134919</t>
+          <t>144408</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121380</t>
+          <t>129386</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>159129</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4189,32 +4189,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>333986</t>
+          <t>353085</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>310797</t>
+          <t>327722</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>357137</t>
+          <t>378170</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -4232,32 +4232,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4267,32 +4267,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4302,32 +4302,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>54381</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>51661</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>40758</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>63043</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>89238</t>
+          <t>94101</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>74188</t>
+          <t>78332</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>108314</t>
+          <t>112313</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>555469</t>
+          <t>594305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>30803</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>28604</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>52155</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>910</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -5479,32 +5479,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5514,32 +5514,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5549,32 +5549,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5705,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5740,32 +5740,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5775,32 +5775,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5931,32 +5931,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6001,32 +6001,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6044,32 +6044,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>405339</t>
+          <t>175461</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>312309</t>
+          <t>158221</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>468185</t>
+          <t>192378</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>28286</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>40834</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6114,32 +6114,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>433625</t>
+          <t>207545</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>324704</t>
+          <t>188236</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>510763</t>
+          <t>225353</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -6270,32 +6270,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>36858</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>59188</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6305,32 +6305,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>32405</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>40301</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>65642</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>123346</t>
+          <t>90996</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>489525</t>
+          <t>271410</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>82970</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>354380</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -6726,32 +6726,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>48580</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>45447</t>
+          <t>47608</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>69983</t>
+          <t>74067</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>55869</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>87483</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6839,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>34596</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6874,32 +6874,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6909,32 +6909,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>43445</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -7404,102 +7404,102 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>17464</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>21722</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>13466</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>34969</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>9442</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>4891</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>17383</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>20500</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>12118</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>33166</t>
-        </is>
-      </c>
-      <c r="U63" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -7517,32 +7517,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7630,32 +7630,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7665,32 +7665,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7700,32 +7700,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>30643</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7743,67 +7743,67 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>15127</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7813,32 +7813,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7856,32 +7856,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7891,32 +7891,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -7969,32 +7969,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>386456</t>
+          <t>410564</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>361332</t>
+          <t>383894</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>410135</t>
+          <t>437621</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8004,32 +8004,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>211984</t>
+          <t>229328</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>192313</t>
+          <t>210874</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>232841</t>
+          <t>249664</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8039,32 +8039,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>598440</t>
+          <t>639892</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>562965</t>
+          <t>606635</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>627883</t>
+          <t>673948</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -8082,32 +8082,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -8127,12 +8127,12 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8152,32 +8152,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -8195,32 +8195,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>75009</t>
+          <t>91973</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>73329</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>96529</t>
+          <t>115758</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8230,32 +8230,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>120373</t>
+          <t>136145</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>104862</t>
+          <t>119073</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>138202</t>
+          <t>154252</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8265,32 +8265,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>195382</t>
+          <t>228118</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>172795</t>
+          <t>201328</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>222585</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>559714</t>
+          <t>620766</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>426452</t>
+          <t>478595</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8378,17 +8378,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>986166</t>
+          <t>1099361</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8651,32 +8651,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8686,32 +8686,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>33471</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>39116</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -8764,32 +8764,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8799,32 +8799,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8834,32 +8834,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>41243</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9364,67 +9364,67 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>8659</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>7227</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="T80" s="2" t="inlineStr">
-        <is>
-          <t>15266</t>
-        </is>
-      </c>
-      <c r="U80" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9512,32 +9512,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9590,32 +9590,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9625,32 +9625,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>706</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -9728,42 +9728,42 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>6738</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
           <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R83" s="2" t="inlineStr">
-        <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="S83" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="T83" s="2" t="inlineStr">
-        <is>
-          <t>5738</t>
-        </is>
-      </c>
-      <c r="U83" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V83" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="W83" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9781,32 +9781,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9816,32 +9816,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9851,32 +9851,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>34663</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>47237</t>
+          <t>59882</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9894,32 +9894,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>187493</t>
+          <t>226270</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>171126</t>
+          <t>206756</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>200772</t>
+          <t>243722</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>170118</t>
+          <t>154647</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>93257</t>
+          <t>139395</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>221956</t>
+          <t>170184</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9964,32 +9964,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>357611</t>
+          <t>380917</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>242971</t>
+          <t>357087</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>414483</t>
+          <t>407545</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -10007,32 +10007,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>69943</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>202038</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10077,32 +10077,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>218812</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -10120,32 +10120,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>65937</t>
+          <t>74608</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>36713</t>
+          <t>62236</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>91665</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10190,32 +10190,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>109393</t>
+          <t>121818</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -10233,17 +10233,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>306885</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>373440</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>619862</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
@@ -10430,12 +10430,12 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -10576,32 +10576,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>94103</t>
+          <t>103824</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>84967</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>116836</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>107286</t>
+          <t>117974</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>88612</t>
+          <t>102228</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>126047</t>
+          <t>137179</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10646,32 +10646,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>201389</t>
+          <t>221798</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>151036</t>
+          <t>197101</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>231339</t>
+          <t>251103</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -10689,32 +10689,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>60649</t>
+          <t>70162</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10724,32 +10724,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>55176</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>68441</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10759,32 +10759,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>91068</t>
+          <t>108830</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>67251</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -11028,32 +11028,32 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11098,32 +11098,32 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -11254,32 +11254,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>46767</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11289,32 +11289,32 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>51382</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11324,32 +11324,32 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>67465</t>
+          <t>76526</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>86705</t>
+          <t>97984</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -11367,102 +11367,102 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>21338</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>10606</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
-          <t>10761</t>
-        </is>
-      </c>
-      <c r="S98" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="T98" s="2" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
-      </c>
-      <c r="U98" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -11480,32 +11480,32 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>68730</t>
+          <t>80265</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>45236</t>
+          <t>62610</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>94663</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -11515,32 +11515,32 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>48349</t>
+          <t>58288</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>62567</t>
+          <t>71947</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11550,32 +11550,32 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>117079</t>
+          <t>138554</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>88462</t>
+          <t>116386</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>167776</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -11593,102 +11593,102 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>8333</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>17731</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>19565</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>11208</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>29664</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
           <t>0,88%</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>1548</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>10034</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R100" s="2" t="inlineStr">
-        <is>
-          <t>13284</t>
-        </is>
-      </c>
-      <c r="S100" s="2" t="inlineStr">
-        <is>
-          <t>7552</t>
-        </is>
-      </c>
-      <c r="T100" s="2" t="inlineStr">
-        <is>
-          <t>22341</t>
-        </is>
-      </c>
-      <c r="U100" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V100" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="W100" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -11706,32 +11706,32 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>64553</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11741,32 +11741,32 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>62501</t>
+          <t>75030</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>47866</t>
+          <t>59232</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>78688</t>
+          <t>91271</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11776,32 +11776,32 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>109396</t>
+          <t>135207</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>113837</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>131888</t>
+          <t>160959</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -11819,32 +11819,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>1377741</t>
+          <t>1233131</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1282843</t>
+          <t>1186898</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1573722</t>
+          <t>1277008</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11854,32 +11854,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>716884</t>
+          <t>740801</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>602963</t>
+          <t>706423</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>780664</t>
+          <t>773080</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11889,32 +11889,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>2094625</t>
+          <t>1973933</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>1947468</t>
+          <t>1913610</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>2387199</t>
+          <t>2032582</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -11932,67 +11932,67 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>48233</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>11607</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>75840</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>5035</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>294725</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12002,32 +12002,32 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>92409</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>401787</t>
+          <t>59242</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -12045,32 +12045,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>239377</t>
+          <t>273959</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>156971</t>
+          <t>241771</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>289661</t>
+          <t>308316</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12080,32 +12080,32 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>331625</t>
+          <t>367365</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>280322</t>
+          <t>341444</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>369808</t>
+          <t>395877</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12115,32 +12115,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>571002</t>
+          <t>641324</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>439786</t>
+          <t>595263</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>642262</t>
+          <t>684267</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -12158,17 +12158,17 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>1943292</t>
+          <t>1901556</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1437829</t>
+          <t>1481121</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12228,17 +12228,17 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>3381120</t>
+          <t>3382677</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
